--- a/Digitised_Records_Low_Frequency_2026_05_06.xlsx
+++ b/Digitised_Records_Low_Frequency_2026_05_06.xlsx
@@ -8023,10 +8023,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -8043,6 +8042,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8381,44 +8384,44 @@
     <col min="14" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>1258</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>1385</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>1386</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>1387</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>1388</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>1389</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>1390</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>1425</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>1426</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>1429</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>1436</v>
       </c>
     </row>
@@ -9062,7 +9065,7 @@
       <c r="H17" s="1">
         <v>39</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="1">
         <v>1900</v>
       </c>
       <c r="J17" s="1">
